--- a/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5343.61</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35267.81</v>
+        <v>35075.04</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>36336.53</v>
+        <v>35931.69</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2229.89</v>
+        <v>2205.04</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2233.63</v>
+        <v>2221.4</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4632.91</v>
+        <v>4683.3</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7432.1</v>
+        <v>7456.55</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3242.03</v>
+        <v>3297.99</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2841.04</v>
+        <v>2890.08</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5877.97</v>
+        <v>5867.54</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5343.61</v>
+        <v>5334.13</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2967.93</v>
+        <v>2955.7</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2671.8</v>
+        <v>2685.6</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5457.54</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17464.14</v>
+        <v>17242.31</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16372.63</v>
+        <v>16209.73</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37111.3</v>
+        <v>36955.72</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5457.54</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2728.77</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2401.32</v>
+        <v>2373.53</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8732.07</v>
+        <v>8743.26</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>37111.3</v>
+        <v>37428.45</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>43660.35</v>
+        <v>44033.47</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3274.53</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4240.51</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2401.32</v>
+        <v>2430.83</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2949.31</v>
+        <v>2985.56</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3360.02</v>
+        <v>3401.31</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7094.81</v>
+        <v>7185.97</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5824.14</v>
+        <v>5855.99</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3141.02</v>
+        <v>3158.2</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>33836.77</v>
+        <v>34021.82</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15936.03</v>
+        <v>16023.18</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>27270.5</v>
+        <v>27419.63</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>37331.77</v>
+        <v>36603.63</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>56563.28</v>
+        <v>55832.24</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>64919.94</v>
+        <v>64792.09</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>38463.03</v>
+        <v>38715.11</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2828.16</v>
+        <v>2846.7</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5656.33</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11312.66</v>
+        <v>11587.75</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3480.2</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>24361.38</v>
+        <v>24530.99</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5800.33</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5220.3</v>
+        <v>5211.35</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6960.4</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13920.79</v>
+        <v>13906.43</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>39442.24</v>
+        <v>39401.56</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2610.15</v>
+        <v>2623.66</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>32970.9</v>
+        <v>33514.31</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>37367.02</v>
+        <v>37458.96</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>36267.99</v>
+        <v>36925.56</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4110.37</v>
+        <v>4127.35</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2417.87</v>
+        <v>2411.2</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>37367.02</v>
+        <v>37152.38</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>75833.08</v>
+        <v>75397.48</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7693.21</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3973.21</v>
+        <v>3947.75</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3297.09</v>
+        <v>3226.15</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8977.780000000001</v>
+        <v>8768.879999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3297.09</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2784.32</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3341.18</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>55686.34</v>
+        <v>54195.25</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7796.09</v>
+        <v>7818.78</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>13364.72</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2338.83</v>
+        <v>2348.55</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>24501.99</v>
+        <v>24461.02</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>37866.71</v>
+        <v>37803.4</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3842.36</v>
+        <v>3835.93</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>28400.04</v>
+        <v>28778.12</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8909.82</v>
+        <v>9011.139999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>14330.1</v>
+        <v>14459.19</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9876.530000000001</v>
+        <v>9939.700000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>36752.99</v>
+        <v>36868.62</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2361.1</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3007.89</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3329.85</v>
+        <v>3301.45</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2361.75</v>
+        <v>2374.47</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>16320.61</v>
+        <v>16503.14</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>37877.19</v>
+        <v>37781.56</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2361.75</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2785.09</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2395.18</v>
+        <v>2371.29</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>11140.35</v>
+        <v>11029.25</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>61271.92</v>
+        <v>61003.34</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6684.21</v>
+        <v>6717.04</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5570.17</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>36763.15</v>
+        <v>36880.16</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3345.06</v>
+        <v>3355.71</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>11069.49</v>
+        <v>11199.34</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6641.69</v>
+        <v>6529.48</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>24352.87</v>
+        <v>24018.25</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2379.94</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3597.58</v>
+        <v>3613.92</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4427.79</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>23522.66</v>
+        <v>23969.86</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2767.37</v>
+        <v>2786.48</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>9829.83</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2374.6</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2767.37</v>
+        <v>2713.2</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>55347.43</v>
+        <v>54527.41</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2363.13</v>
+        <v>2372.35</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2363.13</v>
+        <v>2386.79</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2309.42</v>
+        <v>2318.41</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2685.37</v>
+        <v>2671.77</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>35446.9</v>
+        <v>35522.45</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7227.95</v>
+        <v>7275.07</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10911.2</v>
+        <v>10982.33</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>14071.34</v>
+        <v>14169.82</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2416.83</v>
+        <v>2411.58</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2277.19</v>
+        <v>2272.63</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,68 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2309.42</v>
+        <v>2296.62</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4030-119-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>69.251.100-K</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>8748.809999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1350296-2302-CM25</t>
+          <t>1057448-29-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3179.01</v>
+        <v>24219.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3447-4389-CM25</t>
+          <t>3885-24-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,24 +623,20 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.21</v>
+        <v>11176.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1213005-337-CM25</t>
+          <t>1058345-6-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -695,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5290.28</v>
+        <v>35123.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1058345-94-CM25</t>
+          <t>1260687-65-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -756,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35075.04</v>
+        <v>2634.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2404-1524-CM25</t>
+          <t>1058345-22-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>35931.69</v>
+        <v>33202.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1423-27-CM25</t>
+          <t>1260687-119-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.701.012-9</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2205.04</v>
+        <v>4549.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1346281-186-CM25</t>
+          <t>948-38-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2221.4</v>
+        <v>2452.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3447-4521-CM25</t>
+          <t>1058345-37-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5336.81</v>
+        <v>35170.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1213005-342-CM25</t>
+          <t>1058345-53-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5362.68</v>
+        <v>34612.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1407-15763-CM25</t>
+          <t>1350296-1842-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2252.32</v>
+        <v>4645.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>777-64-CM25</t>
+          <t>1407-15549-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.402.005-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4683.3</v>
+        <v>2592.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>845-182-CM25</t>
+          <t>907562-135-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7456.55</v>
+        <v>14520.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>907562-170-CM25</t>
+          <t>1213005-261-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3297.99</v>
+        <v>5194.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>699-59-CM25</t>
+          <t>1057448-429-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2890.08</v>
+        <v>12403.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1407-15793-CM25</t>
+          <t>1407-15659-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1402,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5867.54</v>
+        <v>7786.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1213005-348-CM25</t>
+          <t>1350296-2302-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5334.13</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>907562-181-CM25</t>
+          <t>3447-4389-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,20 +1538,24 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2955.7</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1249-28-CM25</t>
+          <t>1213005-337-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,22 +1570,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.805.002-7</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Tarapacá</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2685.6</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1213005-354-CM25</t>
+          <t>1058345-94-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5387</v>
+        <v>35075.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3885-2517-CM25</t>
+          <t>2404-1524-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17242.31</v>
+        <v>35931.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5690-197-CM25</t>
+          <t>1423-27-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.701.012-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16209.73</v>
+        <v>2205.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2404-1664-CM25</t>
+          <t>1346281-186-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>36955.72</v>
+        <v>2221.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6-299-CM25</t>
+          <t>3447-4521-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2282.56</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1213005-357-CM25</t>
+          <t>1213005-342-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5434.66</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2038-87-CM25</t>
+          <t>1407-15763-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1992,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.103.002-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERPLAC I Región</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2697.19</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>951-1851-CM25</t>
+          <t>777-64-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>61.402.005-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2373.53</v>
+        <v>4683.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1407-15886-CM25</t>
+          <t>845-182-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2302.56</v>
+        <v>7456.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1350296-2654-CM25</t>
+          <t>907562-170-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2288.95</v>
+        <v>3297.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1407-15890-CM25</t>
+          <t>699-59-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8743.26</v>
+        <v>2890.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1350296-2658-CM25</t>
+          <t>1407-15793-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3278.72</v>
+        <v>5867.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5651-2202-CM25</t>
+          <t>1213005-348-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2358,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3278.72</v>
+        <v>5334.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1213005-360-CM25</t>
+          <t>907562-181-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2419,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5464.54</v>
+        <v>2955.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2404-1789-CM25</t>
+          <t>1249-28-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,27 +2480,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>60.805.002-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Tesorería Regional de Tarapacá</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>37428.45</v>
+        <v>2685.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>628-509-CM25</t>
+          <t>1213005-354-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,22 +2546,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>44033.47</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>628-510-CM25</t>
+          <t>3885-2517-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5504.18</v>
+        <v>17242.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4019-518-CM25</t>
+          <t>5690-197-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3302.51</v>
+        <v>16209.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6-306-CM25</t>
+          <t>1213005-357-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4286</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>614-64-CM25</t>
+          <t>6-299-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2430.83</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5126-141-CM25</t>
+          <t>2404-1664-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2851,22 +2851,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2985.56</v>
+        <v>36955.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>777-76-CM25</t>
+          <t>951-1851-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.402.005-9</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3401.31</v>
+        <v>2373.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>575924-162-CM25</t>
+          <t>2038-87-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.318.000-3</t>
+          <t>60.103.002-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+          <t>SERPLAC I Región</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7185.97</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1350296-2693-CM25</t>
+          <t>1407-15886-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3316.6</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5651-2206-CM25</t>
+          <t>1350296-2654-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5855.99</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>951-1859-CM25</t>
+          <t>1213005-360-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3158.2</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>696217-184-CM25</t>
+          <t>5651-2202-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,22 +3217,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5487.39</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2591-1152-CM25</t>
+          <t>1350296-2658-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>34021.82</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3447-5100-CM25</t>
+          <t>1407-15890-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10974.78</v>
+        <v>8743.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3447-5118-CM25</t>
+          <t>4019-518-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>16023.18</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5690-226-CM25</t>
+          <t>628-509-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>27419.63</v>
+        <v>44033.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1058345-1-CM26</t>
+          <t>2404-1789-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,27 +3517,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>36603.63</v>
+        <v>37428.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3447-75-CM26</t>
+          <t>628-510-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>55832.24</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1423-1-CM26</t>
+          <t>6-306-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,27 +3639,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.701.012-9</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2370.98</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057448-7-CM26</t>
+          <t>5126-141-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>64792.09</v>
+        <v>2985.56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1423-2-CM26</t>
+          <t>614-64-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,27 +3761,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.701.012-9</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2370.98</v>
+        <v>2430.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1091793-14-CM26</t>
+          <t>777-76-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>61.402.005-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3372.53</v>
+        <v>3401.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2404-26-CM26</t>
+          <t>1350296-2693-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>38715.11</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1233607-20-CM26</t>
+          <t>575924-162-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2846.7</v>
+        <v>7185.97</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>722640-7-CM26</t>
+          <t>5651-2206-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5732.5</v>
+        <v>5855.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1070620-1034-CM26</t>
+          <t>696217-184-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11587.75</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1288512-4-CM26</t>
+          <t>951-1859-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,28 +4172,28 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2446.27</v>
+        <v>3158.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1350296-218-CM26</t>
+          <t>3447-5100-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4233,43 +4233,43 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3498.18</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1407-50-CM26</t>
+          <t>2591-1152-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4294,28 +4294,28 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9345.139999999999</v>
+        <v>34021.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5651-8-CM26</t>
+          <t>3447-5118-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,28 +4355,28 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3504.43</v>
+        <v>16023.18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3885-31-CM26</t>
+          <t>5690-226-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,28 +4416,28 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>24530.99</v>
+        <v>27419.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>907562-8-CM26</t>
+          <t>1058345-1-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,43 +4477,43 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5790.39</v>
+        <v>36603.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2013-190-CM26</t>
+          <t>3447-75-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,43 +4538,43 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5211.35</v>
+        <v>55832.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1534-1-CM26</t>
+          <t>1423-2-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.701.012-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,43 +4599,43 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6953.22</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3885-51-CM26</t>
+          <t>1423-1-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.701.012-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4660,43 +4660,43 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13906.43</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2404-150-CM26</t>
+          <t>1057448-7-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4721,28 +4721,28 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>39401.56</v>
+        <v>64792.09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1430-4-CM26</t>
+          <t>1091793-14-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>62.000.710-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,43 +4782,43 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4607.02</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1350296-325-CM26</t>
+          <t>2404-26-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,43 +4843,43 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2623.66</v>
+        <v>38715.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2591-147-CM26</t>
+          <t>1233607-20-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,28 +4904,28 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>33514.31</v>
+        <v>2846.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3447-587-CM26</t>
+          <t>722640-7-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,43 +4965,43 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>37458.96</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1058345-8-CM26</t>
+          <t>1070620-1034-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,43 +5026,43 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>36925.56</v>
+        <v>11587.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2013-278-CM26</t>
+          <t>1288512-4-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3310.71</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5690-29-CM26</t>
+          <t>1350296-218-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4127.35</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2013-336-CM26</t>
+          <t>3885-31-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,27 +5164,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2411.2</v>
+        <v>24530.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>575924-17-CM26</t>
+          <t>1407-50-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.318.000-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2281.32</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2404-308-CM26</t>
+          <t>5651-8-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,27 +5286,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>37152.38</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1024-47-CM26</t>
+          <t>2013-190-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,27 +5347,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>75397.48</v>
+        <v>5211.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1407-170-CM26</t>
+          <t>907562-8-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7643.92</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2174-41-CM26</t>
+          <t>2404-150-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5469,27 +5469,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3947.75</v>
+        <v>39401.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>951-10-CM26</t>
+          <t>1534-1-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3226.15</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3447-864-CM26</t>
+          <t>3885-51-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8768.879999999999</v>
+        <v>13906.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6-50-CM26</t>
+          <t>1430-4-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3220.37</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>548847-12-CM26</t>
+          <t>1350296-325-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2711</v>
+        <v>2623.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2270-34-CM26</t>
+          <t>2591-147-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,27 +5774,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3253.2</v>
+        <v>33514.31</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4019-103-CM26</t>
+          <t>3447-587-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3280.59</v>
+        <v>37458.96</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3447-946-CM26</t>
+          <t>1058345-8-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>54195.25</v>
+        <v>36925.56</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4030-56-CM26</t>
+          <t>2013-278-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5957,27 +5957,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7818.78</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707412-31-CM26</t>
+          <t>5690-29-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6018,27 +6018,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>13420.27</v>
+        <v>4127.35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1407-198-CM26</t>
+          <t>2013-336-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2348.55</v>
+        <v>2411.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3885-143-CM26</t>
+          <t>575924-17-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>24461.02</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2404-424-CM26</t>
+          <t>2404-308-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>37803.4</v>
+        <v>37152.38</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1350296-677-CM26</t>
+          <t>1024-47-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3835.93</v>
+        <v>75397.48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>600644-30-CM26</t>
+          <t>1407-170-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.979.010-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>28778.12</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1407-225-CM26</t>
+          <t>2174-41-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9011.139999999999</v>
+        <v>3947.75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5690-50-CM26</t>
+          <t>951-10-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>14459.19</v>
+        <v>3226.15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>575924-20-CM26</t>
+          <t>3447-864-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.318.000-3</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9939.700000000001</v>
+        <v>8768.879999999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1312459-37-CM26</t>
+          <t>6-50-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3351.69</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1058345-22-CM26</t>
+          <t>548847-12-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>36868.62</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1312459-41-CM26</t>
+          <t>2270-34-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2350.96</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>907562-56-CM26</t>
+          <t>4019-103-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5544.71</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3885-197-CM26</t>
+          <t>3447-946-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2967</v>
+        <v>54195.25</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>819-9-CM26</t>
+          <t>4030-56-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3301.45</v>
+        <v>7818.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1350296-847-CM26</t>
+          <t>1407-198-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2374.47</v>
+        <v>2348.55</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3447-1197-CM26</t>
+          <t>707412-31-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,27 +6994,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>16503.14</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2948-130-CM26</t>
+          <t>3885-143-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3928.66</v>
+        <v>24461.02</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5651-34-CM26</t>
+          <t>2404-424-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,27 +7116,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4489.89</v>
+        <v>37803.4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2404-599-CM26</t>
+          <t>1350296-677-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7177,27 +7177,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>37781.56</v>
+        <v>3835.93</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>935934-107-CM26</t>
+          <t>600644-30-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.979.010-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2355.79</v>
+        <v>28778.12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3159-68-CM26</t>
+          <t>1407-225-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2805.84</v>
+        <v>9011.139999999999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1407-291-CM26</t>
+          <t>5690-50-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2371.29</v>
+        <v>14459.19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1407-292-CM26</t>
+          <t>575924-20-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>11029.25</v>
+        <v>9939.700000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3447-1362-CM26</t>
+          <t>1312459-37-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>61003.34</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>951-26-CM26</t>
+          <t>1058345-22-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3305.75</v>
+        <v>36868.62</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5651-43-CM26</t>
+          <t>1312459-41-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6717.04</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2270-72-CM26</t>
+          <t>907562-56-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5597.54</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1058345-30-CM26</t>
+          <t>3885-197-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>36880.16</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5651-45-CM26</t>
+          <t>819-9-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3355.71</v>
+        <v>3301.45</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1070620-4874-CM26</t>
+          <t>1350296-847-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,27 +7848,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>11199.34</v>
+        <v>2374.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6-92-CM26</t>
+          <t>3447-1197-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6529.48</v>
+        <v>16503.14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4019-197-CM26</t>
+          <t>5651-34-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3275.22</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5690-77-CM26</t>
+          <t>2948-130-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>24018.25</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4428-1-CM26</t>
+          <t>935934-107-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8092,27 +8092,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2365.18</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5690-79-CM26</t>
+          <t>2404-599-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3613.92</v>
+        <v>37781.56</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>907562-64-CM26</t>
+          <t>3159-68-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5617.16</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1407-348-CM26</t>
+          <t>1407-291-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4511.97</v>
+        <v>2371.29</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3885-297-CM26</t>
+          <t>1407-292-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>23969.86</v>
+        <v>11029.25</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2948-173-CM26</t>
+          <t>3447-1362-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8397,27 +8397,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3395.74</v>
+        <v>61003.34</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>699-22-CM26</t>
+          <t>951-26-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2786.48</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3159-95-CM26</t>
+          <t>5651-43-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8519,27 +8519,27 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2387.3</v>
+        <v>6717.04</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1407-374-CM26</t>
+          <t>2270-72-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>9829.83</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1350296-1117-CM26</t>
+          <t>1058345-30-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8641,27 +8641,27 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2328.12</v>
+        <v>36880.16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>696217-58-CM26</t>
+          <t>5651-45-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8702,27 +8702,27 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2713.2</v>
+        <v>3355.71</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3447-1796-CM26</t>
+          <t>1070620-4874-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>54527.41</v>
+        <v>11199.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1346281-98-CM26</t>
+          <t>6-92-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2372.35</v>
+        <v>6529.48</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1346281-107-CM26</t>
+          <t>4019-197-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2386.79</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>575924-32-CM26</t>
+          <t>5690-77-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.318.000-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2318.41</v>
+        <v>24018.25</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>696217-63-CM26</t>
+          <t>4428-1-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2671.77</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1058345-50-CM26</t>
+          <t>5690-79-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>35522.45</v>
+        <v>3613.92</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5690-92-CM26</t>
+          <t>907562-64-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9129,27 +9129,27 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7275.07</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5690-93-CM26</t>
+          <t>1407-348-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10982.33</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3447-1999-CM26</t>
+          <t>3885-297-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>14169.82</v>
+        <v>23969.86</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1350296-1310-CM26</t>
+          <t>2948-173-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9312,27 +9312,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2411.58</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2270-74-CM26</t>
+          <t>699-22-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9373,27 +9373,27 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2272.63</v>
+        <v>2786.48</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5690-101-CM26</t>
+          <t>3159-95-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2296.62</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4030-119-CM26</t>
+          <t>1407-374-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,6 +9540,921 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
+        <v>9829.83</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1350296-1117-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>2328.12</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>696217-58-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>2713.2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>3447-1796-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>54527.41</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1346281-98-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>2372.35</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1346281-107-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>2386.79</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>575924-32-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>60.318.000-3</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>2318.41</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>696217-63-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>2671.77</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1058345-50-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>69.010.200-5</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>35522.45</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>5690-92-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>7275.07</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>5690-93-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>10982.33</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>3447-1999-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>14169.82</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1350296-1310-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>2411.58</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2270-74-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>2272.63</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>5690-101-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>2296.62</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4030-119-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>69.251.100-K</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
         <v>8748.809999999999</v>
       </c>
     </row>

--- a/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M353"/>
+  <dimension ref="A1:M370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1489,7 +1489,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2038-5-CM25</t>
+          <t>1407-15071-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.103.002-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2126.93</v>
+        <v>4030.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1407-15071-CM25</t>
+          <t>2038-5-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.103.002-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4030.63</v>
+        <v>2126.93</v>
       </c>
     </row>
     <row r="19">
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>548847-23-CM25</t>
+          <t>3447-886-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2506.1</v>
+        <v>54480.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3447-886-CM25</t>
+          <t>548847-23-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>54480.47</v>
+        <v>2506.1</v>
       </c>
     </row>
     <row r="40">
@@ -4609,7 +4609,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2404-470-CM25</t>
+          <t>6-80-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4629,17 +4629,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>34114.41</v>
+        <v>2238.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6-80-CM25</t>
+          <t>2404-470-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2238.76</v>
+        <v>34114.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>948-38-CM25</t>
+          <t>696217-38-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2452.52</v>
+        <v>2665.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>696217-38-CM25</t>
+          <t>948-38-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2665.79</v>
+        <v>2452.52</v>
       </c>
     </row>
     <row r="69">
@@ -5389,7 +5389,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1312459-196-CM25</t>
+          <t>1213005-136-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2250.18</v>
+        <v>5357.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1213005-136-CM25</t>
+          <t>1312459-196-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5357.56</v>
+        <v>2250.18</v>
       </c>
     </row>
     <row r="79">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4030-69-CM25</t>
+          <t>525512-61-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3705.82</v>
+        <v>2223.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4019-214-CM25</t>
+          <t>2013-621-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5779,7 +5779,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2013-621-CM25</t>
+          <t>4019-214-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>525512-61-CM25</t>
+          <t>1213005-141-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5864,17 +5864,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2223.49</v>
+        <v>5294.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1213005-141-CM25</t>
+          <t>4030-69-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5294.03</v>
+        <v>3705.82</v>
       </c>
     </row>
     <row r="86">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1260687-162-CM25</t>
+          <t>1213005-144-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4998.88</v>
+        <v>5317.96</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1213005-144-CM25</t>
+          <t>819-20-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5317.96</v>
+        <v>2233.54</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>819-20-CM25</t>
+          <t>1260687-162-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2233.54</v>
+        <v>4998.88</v>
       </c>
     </row>
     <row r="96">
@@ -6949,7 +6949,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1407-15381-CM25</t>
+          <t>696217-58-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6969,17 +6969,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2210.69</v>
+        <v>2242.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>696217-58-CM25</t>
+          <t>1407-15381-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2242.73</v>
+        <v>2210.69</v>
       </c>
     </row>
     <row r="103">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1213005-165-CM25</t>
+          <t>908366-47-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5331.12</v>
+        <v>10662.23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>908366-47-CM25</t>
+          <t>1213005-165-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10662.23</v>
+        <v>5331.12</v>
       </c>
     </row>
     <row r="110">
@@ -9159,7 +9159,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>819-28-CM25</t>
+          <t>907562-135-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2136.6</v>
+        <v>14520.56</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1407-15549-CM25</t>
+          <t>819-28-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2592.96</v>
+        <v>2136.6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>907562-135-CM25</t>
+          <t>1407-15549-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>14520.56</v>
+        <v>2592.96</v>
       </c>
     </row>
     <row r="138">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3447-2751-CM25</t>
+          <t>1058345-72-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6201.68</v>
+        <v>34109.23</v>
       </c>
     </row>
     <row r="142">
@@ -9679,7 +9679,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1058345-72-CM25</t>
+          <t>3447-2751-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>34109.23</v>
+        <v>6201.68</v>
       </c>
     </row>
     <row r="144">
@@ -9939,7 +9939,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3447-2869-CM25</t>
+          <t>2404-1133-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>51481.64</v>
+        <v>35007.52</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2404-1133-CM25</t>
+          <t>3447-2869-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>35007.52</v>
+        <v>51481.64</v>
       </c>
     </row>
     <row r="149">
@@ -11109,7 +11109,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1213005-323-CM25</t>
+          <t>2404-1363-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5229.41</v>
+        <v>35560.02</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2404-1363-CM25</t>
+          <t>1213005-323-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>35560.02</v>
+        <v>5229.41</v>
       </c>
     </row>
     <row r="167">
@@ -13254,7 +13254,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6-299-CM25</t>
+          <t>1213005-357-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2282.56</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1213005-357-CM25</t>
+          <t>2404-1664-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5434.66</v>
+        <v>36955.72</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2404-1664-CM25</t>
+          <t>6-299-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13404,17 +13404,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>36955.72</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="201">
@@ -13969,7 +13969,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4019-518-CM25</t>
+          <t>2404-1789-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3302.51</v>
+        <v>37428.45</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2404-1789-CM25</t>
+          <t>4019-518-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14054,17 +14054,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>37428.45</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="211">
@@ -14164,7 +14164,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5126-141-CM25</t>
+          <t>614-64-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2985.56</v>
+        <v>2430.83</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>614-64-CM25</t>
+          <t>5126-141-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2430.83</v>
+        <v>2985.56</v>
       </c>
     </row>
     <row r="214">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3885-31-CM26</t>
+          <t>5651-8-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15684,12 +15684,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>24530.99</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="236">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1407-50-CM26</t>
+          <t>3885-31-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>9345.139999999999</v>
+        <v>24530.99</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5651-8-CM26</t>
+          <t>1407-50-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3504.43</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>907562-8-CM26</t>
+          <t>2013-190-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15939,17 +15939,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5790.39</v>
+        <v>5211.35</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2013-190-CM26</t>
+          <t>907562-8-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5211.35</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1534-1-CM26</t>
+          <t>2404-150-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16089,17 +16089,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>6953.22</v>
+        <v>39401.56</v>
       </c>
     </row>
     <row r="242">
@@ -16179,7 +16179,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2404-150-CM26</t>
+          <t>1534-1-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16219,17 +16219,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16238,7 +16238,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>39401.56</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="244">
@@ -16569,7 +16569,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2013-278-CM26</t>
+          <t>5690-29-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16589,17 +16589,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3310.71</v>
+        <v>4127.35</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5690-29-CM26</t>
+          <t>2013-278-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16654,17 +16654,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4127.35</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="251">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2404-308-CM26</t>
+          <t>1024-47-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16849,17 +16849,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>37152.38</v>
+        <v>75397.48</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1024-47-CM26</t>
+          <t>2404-308-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16914,17 +16914,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>75397.48</v>
+        <v>37152.38</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1407-170-CM26</t>
+          <t>2174-41-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7643.92</v>
+        <v>3947.75</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2174-41-CM26</t>
+          <t>1407-170-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3947.75</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="257">
@@ -17609,7 +17609,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1407-198-CM26</t>
+          <t>707412-31-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17629,17 +17629,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2348.55</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>707412-31-CM26</t>
+          <t>1407-198-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17694,17 +17694,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>13420.27</v>
+        <v>2348.55</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3885-143-CM26</t>
+          <t>1350296-677-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>24461.02</v>
+        <v>3835.93</v>
       </c>
     </row>
     <row r="268">
@@ -17869,7 +17869,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1350296-677-CM26</t>
+          <t>3885-143-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3835.93</v>
+        <v>24461.02</v>
       </c>
     </row>
     <row r="270">
@@ -18194,7 +18194,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1312459-37-CM26</t>
+          <t>1058345-22-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3351.69</v>
+        <v>36868.62</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1058345-22-CM26</t>
+          <t>1312459-37-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>36868.62</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1312459-41-CM26</t>
+          <t>907562-56-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2350.96</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>907562-56-CM26</t>
+          <t>1312459-41-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>5544.71</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="278">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>935934-107-CM26</t>
+          <t>2404-599-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18864,17 +18864,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2355.79</v>
+        <v>37781.56</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2404-599-CM26</t>
+          <t>935934-107-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18929,17 +18929,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>37781.56</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="286">
@@ -19299,7 +19299,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5651-43-CM26</t>
+          <t>2270-72-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>6717.04</v>
+        <v>5597.54</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2270-72-CM26</t>
+          <t>5651-43-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>5597.54</v>
+        <v>6717.04</v>
       </c>
     </row>
     <row r="293">
@@ -19689,7 +19689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4019-197-CM26</t>
+          <t>5690-77-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3275.22</v>
+        <v>24018.25</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5690-77-CM26</t>
+          <t>4019-197-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>24018.25</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="299">
@@ -20014,7 +20014,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3885-297-CM26</t>
+          <t>1407-348-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>23969.86</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1407-348-CM26</t>
+          <t>3885-297-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20138,7 +20138,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4511.97</v>
+        <v>23969.86</v>
       </c>
     </row>
     <row r="304">
@@ -20924,7 +20924,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5690-92-CM26</t>
+          <t>5690-93-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -20983,13 +20983,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>7275.07</v>
+        <v>10982.33</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5690-93-CM26</t>
+          <t>5690-92-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>10982.33</v>
+        <v>7275.07</v>
       </c>
     </row>
     <row r="318">
@@ -21249,7 +21249,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2270-74-CM26</t>
+          <t>2013-1195-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2272.63</v>
+        <v>5359.98</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2013-1195-CM26</t>
+          <t>2270-74-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21373,7 +21373,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>5359.98</v>
+        <v>2272.63</v>
       </c>
     </row>
     <row r="323">
@@ -21834,7 +21834,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>696217-104-CM26</t>
+          <t>3447-2370-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21854,17 +21854,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3828.53</v>
+        <v>54693.23</v>
       </c>
     </row>
     <row r="331">
@@ -21964,7 +21964,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3447-2370-CM26</t>
+          <t>696217-104-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21984,17 +21984,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>54693.23</v>
+        <v>3828.53</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2270-204-CM26</t>
+          <t>1058345-60-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>10933.26</v>
+        <v>36079.77</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1058345-60-CM26</t>
+          <t>2270-204-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>36079.77</v>
+        <v>10933.26</v>
       </c>
     </row>
     <row r="335">
@@ -22484,7 +22484,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1305552-109-CM26</t>
+          <t>696217-130-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22504,17 +22504,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22543,13 +22543,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2355.91</v>
+        <v>3212.61</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>5562-30-CM26</t>
+          <t>1305552-109-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22564,22 +22564,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.979.010-3</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2321.62</v>
+        <v>2355.91</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1407-537-CM26</t>
+          <t>5562-30-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22629,22 +22629,22 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.979.010-3</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,13 +22673,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>12959.38</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3447-2611-CM26</t>
+          <t>1407-537-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>6376.81</v>
+        <v>12959.38</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1305552-117-CM26</t>
+          <t>3447-2611-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22769,12 +22769,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2338.16</v>
+        <v>6376.81</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1350296-1720-CM26</t>
+          <t>951-50-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22868,13 +22868,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2297.58</v>
+        <v>3188.4</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3447-2653-CM26</t>
+          <t>1305552-117-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22933,13 +22933,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>11122.37</v>
+        <v>2338.16</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3885-494-CM26</t>
+          <t>1350296-1720-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22954,22 +22954,22 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>13824.16</v>
+        <v>2297.58</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1057448-418-CM26</t>
+          <t>3447-2653-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23019,22 +23019,22 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>29039.07</v>
+        <v>11122.37</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1070620-8544-CM26</t>
+          <t>3885-494-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23084,22 +23084,22 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -23128,13 +23128,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>10423.29</v>
+        <v>13824.16</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1350296-1785-CM26</t>
+          <t>1057448-418-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23149,22 +23149,22 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2242.71</v>
+        <v>29039.07</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5690-140-CM26</t>
+          <t>1070620-8544-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23214,7 +23214,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>11929.05</v>
+        <v>10423.29</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2591-920-CM26</t>
+          <t>1350296-1785-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23279,22 +23279,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23323,72 +23323,1177 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>20710.15</v>
+        <v>2242.71</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
+          <t>2591-920-CM26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>83.017.500-8</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>20710.15</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>5690-140-CM26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>11929.05</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
           <t>907562-103-CM26</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C355" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
+      <c r="E355" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
+      <c r="F355" t="inlineStr">
         <is>
           <t>69.010.400-8</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
+      <c r="G355" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M353" s="2" t="n">
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="n">
         <v>5156.23</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1523365-3-CM26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>60.511.010-K</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>3091.32</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>696217-152-CM26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>3084.52</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1501513-127-CM26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>61.981.030-9</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>4009.87</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>696217-153-CM26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>2236.14</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>3447-2834-CM26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>55847.77</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2591-963-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>83.017.500-8</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>5166.41</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1058345-74-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>69.010.200-5</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>17349.59</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>6-162-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>61.838.000-9</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>4291.8</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2038-52-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>60.103.002-0</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>2220.7</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1346281-151-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>2248.09</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1233607-73-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>3545.99</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1350296-1935-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>2199.52</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>907562-110-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>3048.5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>5690-172-CM26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>18332.55</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1407-652-CM26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>12163.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M371"/>
+  <dimension ref="A1:M372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8314,7 +8314,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1213005-218-CM25</t>
+          <t>3885-277-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8334,17 +8334,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5155.97</v>
+        <v>16911.58</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3885-277-CM25</t>
+          <t>1213005-218-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>16911.58</v>
+        <v>5155.97</v>
       </c>
     </row>
     <row r="124">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1417913-119-CM26</t>
+          <t>1407-50-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15809,17 +15809,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4672.57</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3885-31-CM26</t>
+          <t>1417913-119-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>24530.99</v>
+        <v>4672.57</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1407-50-CM26</t>
+          <t>3885-31-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>9345.139999999999</v>
+        <v>24530.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2013-190-CM26</t>
+          <t>907562-8-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5211.35</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>907562-8-CM26</t>
+          <t>2013-190-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>5790.39</v>
+        <v>5211.35</v>
       </c>
     </row>
     <row r="242">
@@ -17024,7 +17024,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2174-41-CM26</t>
+          <t>1407-170-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3947.75</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1407-170-CM26</t>
+          <t>2174-41-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>7643.92</v>
+        <v>3947.75</v>
       </c>
     </row>
     <row r="258">
@@ -17674,7 +17674,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>707412-31-CM26</t>
+          <t>1407-198-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17694,17 +17694,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>13420.27</v>
+        <v>2348.55</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1407-198-CM26</t>
+          <t>707412-31-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2348.55</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1350296-677-CM26</t>
+          <t>2404-424-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17824,17 +17824,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3835.93</v>
+        <v>37803.4</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2404-424-CM26</t>
+          <t>3885-143-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17889,17 +17889,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>37803.4</v>
+        <v>24461.02</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3885-143-CM26</t>
+          <t>1350296-677-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>24461.02</v>
+        <v>3835.93</v>
       </c>
     </row>
     <row r="271">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1058345-22-CM26</t>
+          <t>1312459-37-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.010.200-5</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>36868.62</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1312459-37-CM26</t>
+          <t>1058345-22-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3351.69</v>
+        <v>36868.62</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>907562-56-CM26</t>
+          <t>1312459-41-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,13 +18448,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>5544.71</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1312459-41-CM26</t>
+          <t>907562-56-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18479,12 +18479,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2350.96</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="279">
@@ -18779,7 +18779,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2948-130-CM26</t>
+          <t>5651-34-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18819,17 +18819,17 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3928.66</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5651-34-CM26</t>
+          <t>2948-130-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18884,17 +18884,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4489.89</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2404-599-CM26</t>
+          <t>935934-107-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18929,17 +18929,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>37781.56</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>935934-107-CM26</t>
+          <t>2404-599-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18994,17 +18994,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2355.79</v>
+        <v>37781.56</v>
       </c>
     </row>
     <row r="287">
@@ -20469,7 +20469,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>696217-58-CM26</t>
+          <t>1350296-1117-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20489,17 +20489,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,13 +20528,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2713.2</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1350296-1117-CM26</t>
+          <t>696217-58-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20554,17 +20554,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2328.12</v>
+        <v>2713.2</v>
       </c>
     </row>
     <row r="311">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>696217-130-CM26</t>
+          <t>1305552-109-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22569,17 +22569,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3212.61</v>
+        <v>2355.91</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1305552-109-CM26</t>
+          <t>696217-130-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22634,17 +22634,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2355.91</v>
+        <v>3212.61</v>
       </c>
     </row>
     <row r="343">
@@ -24499,65 +24499,130 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
+          <t>5690-173-CM26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>10984.48</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
           <t>1407-652-CM26</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C372" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
         <is>
           <t>61.004.002-0</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
+      <c r="G372" t="inlineStr">
         <is>
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M371" s="2" t="n">
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="n">
         <v>12163.23</v>
       </c>
     </row>
